--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/152.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/152.xlsx
@@ -426,13 +426,13 @@
         <v>-14.03054816793817</v>
       </c>
       <c r="E2">
-        <v>-19.59897945888647</v>
+        <v>-20.51056127663051</v>
       </c>
       <c r="F2">
-        <v>-0.424444835665738</v>
+        <v>0.1813203651838732</v>
       </c>
       <c r="G2">
-        <v>-11.08691222423028</v>
+        <v>-11.0677441655579</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.40901380523261</v>
       </c>
       <c r="E3">
-        <v>-22.26310788844299</v>
+        <v>-20.12497982877342</v>
       </c>
       <c r="F3">
-        <v>-0.6697078562866157</v>
+        <v>-0.1945099254662625</v>
       </c>
       <c r="G3">
-        <v>-10.72175243015759</v>
+        <v>-11.34815068327971</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.78973837572609</v>
       </c>
       <c r="E4">
-        <v>-21.21602507144143</v>
+        <v>-20.47051145250668</v>
       </c>
       <c r="F4">
-        <v>-0.6413826613152893</v>
+        <v>-0.2303550397202027</v>
       </c>
       <c r="G4">
-        <v>-9.778862712935608</v>
+        <v>-11.12037852908677</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.24585788016582</v>
       </c>
       <c r="E5">
-        <v>-21.56919170235163</v>
+        <v>-20.34649466333262</v>
       </c>
       <c r="F5">
-        <v>-0.393292422748657</v>
+        <v>-0.04040211058424804</v>
       </c>
       <c r="G5">
-        <v>-9.330551946553044</v>
+        <v>-10.59245907412136</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.77848874153182</v>
       </c>
       <c r="E6">
-        <v>-22.14552606083383</v>
+        <v>-21.90021409536432</v>
       </c>
       <c r="F6">
-        <v>-0.8655769854133644</v>
+        <v>0.07977329037689024</v>
       </c>
       <c r="G6">
-        <v>-9.449907044880387</v>
+        <v>-10.43932979020237</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.39459413412428</v>
       </c>
       <c r="E7">
-        <v>-21.07747188070275</v>
+        <v>-22.61030146213707</v>
       </c>
       <c r="F7">
-        <v>-0.4148548262435282</v>
+        <v>-0.0533760008468939</v>
       </c>
       <c r="G7">
-        <v>-9.180302837253221</v>
+        <v>-10.20882974648507</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.09487598263043</v>
       </c>
       <c r="E8">
-        <v>-22.48465442232025</v>
+        <v>-21.54872752831097</v>
       </c>
       <c r="F8">
-        <v>-0.7895312011015642</v>
+        <v>0.03775518223728812</v>
       </c>
       <c r="G8">
-        <v>-9.439051766057117</v>
+        <v>-10.33935793600746</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.88082916693828</v>
       </c>
       <c r="E9">
-        <v>-23.10450741601616</v>
+        <v>-22.68043393909386</v>
       </c>
       <c r="F9">
-        <v>-0.07907112931433176</v>
+        <v>0.5127012893671903</v>
       </c>
       <c r="G9">
-        <v>-8.621221217126642</v>
+        <v>-9.618125795367375</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.72990791345352</v>
       </c>
       <c r="E10">
-        <v>-25.12982213120665</v>
+        <v>-22.94852865729596</v>
       </c>
       <c r="F10">
-        <v>-0.08702676985081821</v>
+        <v>0.07220201231530275</v>
       </c>
       <c r="G10">
-        <v>-7.953686125133539</v>
+        <v>-9.282165012951056</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.63269176534252</v>
       </c>
       <c r="E11">
-        <v>-23.28081902303079</v>
+        <v>-23.81363021782527</v>
       </c>
       <c r="F11">
-        <v>-0.1463254503802208</v>
+        <v>0.3604573011414747</v>
       </c>
       <c r="G11">
-        <v>-8.777243917846954</v>
+        <v>-9.764362523473601</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.57338184500595</v>
       </c>
       <c r="E12">
-        <v>-23.95617752263872</v>
+        <v>-23.87702432545865</v>
       </c>
       <c r="F12">
-        <v>-0.1820082046232123</v>
+        <v>0.6044901961691951</v>
       </c>
       <c r="G12">
-        <v>-9.193952216511637</v>
+        <v>-9.145118359261847</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.52610248399473</v>
       </c>
       <c r="E13">
-        <v>-25.62707121961889</v>
+        <v>-24.38011061686678</v>
       </c>
       <c r="F13">
-        <v>0.02556741263989899</v>
+        <v>0.9880309306045886</v>
       </c>
       <c r="G13">
-        <v>-8.202688807869821</v>
+        <v>-9.702514911708937</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.47972939666751</v>
       </c>
       <c r="E14">
-        <v>-24.84854955364223</v>
+        <v>-24.56285718544632</v>
       </c>
       <c r="F14">
-        <v>0.3868971319040294</v>
+        <v>1.272492296725939</v>
       </c>
       <c r="G14">
-        <v>-8.244964474406315</v>
+        <v>-8.622379908065387</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.42181370020581</v>
       </c>
       <c r="E15">
-        <v>-26.18502450210396</v>
+        <v>-25.6861134637309</v>
       </c>
       <c r="F15">
-        <v>0.5579293211926405</v>
+        <v>1.361796929686948</v>
       </c>
       <c r="G15">
-        <v>-9.219264647704904</v>
+        <v>-9.136501009223123</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.33420609769552</v>
       </c>
       <c r="E16">
-        <v>-25.89497121343866</v>
+        <v>-25.14103463284964</v>
       </c>
       <c r="F16">
-        <v>1.123856676906818</v>
+        <v>1.870537113381459</v>
       </c>
       <c r="G16">
-        <v>-8.451456441872816</v>
+        <v>-8.16008539732494</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.21433444830874</v>
       </c>
       <c r="E17">
-        <v>-27.20451532697678</v>
+        <v>-27.37120392672512</v>
       </c>
       <c r="F17">
-        <v>1.957595213946075</v>
+        <v>2.114478059627468</v>
       </c>
       <c r="G17">
-        <v>-7.940539948797093</v>
+        <v>-9.062023666226139</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.06150696500897</v>
       </c>
       <c r="E18">
-        <v>-29.5066805648632</v>
+        <v>-27.37224547574688</v>
       </c>
       <c r="F18">
-        <v>2.097408720925382</v>
+        <v>2.313123876288401</v>
       </c>
       <c r="G18">
-        <v>-7.72624833604007</v>
+        <v>-8.530952571907335</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.871594325569573</v>
       </c>
       <c r="E19">
-        <v>-30.33897559544394</v>
+        <v>-28.49035740755874</v>
       </c>
       <c r="F19">
-        <v>2.002882059857125</v>
+        <v>2.625077099773861</v>
       </c>
       <c r="G19">
-        <v>-7.527724851686594</v>
+        <v>-8.869724007486495</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.65458448713045</v>
       </c>
       <c r="E20">
-        <v>-29.02269311258242</v>
+        <v>-29.34681411120742</v>
       </c>
       <c r="F20">
-        <v>2.179776605255348</v>
+        <v>3.339409789169181</v>
       </c>
       <c r="G20">
-        <v>-8.259401763503076</v>
+        <v>-9.352951097671752</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.422593248188022</v>
       </c>
       <c r="E21">
-        <v>-31.65215607361022</v>
+        <v>-30.73287358581613</v>
       </c>
       <c r="F21">
-        <v>2.465800272298378</v>
+        <v>3.316425907211106</v>
       </c>
       <c r="G21">
-        <v>-6.771510176333034</v>
+        <v>-8.792505532782993</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.183402855212991</v>
       </c>
       <c r="E22">
-        <v>-29.20873188176553</v>
+        <v>-31.19595080936649</v>
       </c>
       <c r="F22">
-        <v>2.049128155220615</v>
+        <v>3.525714588263207</v>
       </c>
       <c r="G22">
-        <v>-6.438664617269169</v>
+        <v>-7.948601127185219</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.954541723395598</v>
       </c>
       <c r="E23">
-        <v>-32.09368681783209</v>
+        <v>-31.63311384040796</v>
       </c>
       <c r="F23">
-        <v>2.510929728402895</v>
+        <v>4.043300079084811</v>
       </c>
       <c r="G23">
-        <v>-5.827587568902797</v>
+        <v>-7.904448381327959</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.752597004555101</v>
       </c>
       <c r="E24">
-        <v>-31.83567021853406</v>
+        <v>-32.66992154988611</v>
       </c>
       <c r="F24">
-        <v>2.456209434508765</v>
+        <v>3.947626957531079</v>
       </c>
       <c r="G24">
-        <v>-6.869475839931146</v>
+        <v>-7.789728046755594</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.586087519240539</v>
       </c>
       <c r="E25">
-        <v>-31.29790940164919</v>
+        <v>-31.13921129428739</v>
       </c>
       <c r="F25">
-        <v>3.038437403975231</v>
+        <v>4.182989330953697</v>
       </c>
       <c r="G25">
-        <v>-7.408647839184549</v>
+        <v>-7.921755913407268</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.468373692820942</v>
       </c>
       <c r="E26">
-        <v>-31.52071711553759</v>
+        <v>-31.86188781880146</v>
       </c>
       <c r="F26">
-        <v>3.128000487565914</v>
+        <v>4.216993812838616</v>
       </c>
       <c r="G26">
-        <v>-6.911787922468572</v>
+        <v>-7.879857649062252</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.408842766659992</v>
       </c>
       <c r="E27">
-        <v>-33.87293557663079</v>
+        <v>-33.10741063105613</v>
       </c>
       <c r="F27">
-        <v>3.590058854643061</v>
+        <v>3.88433471775278</v>
       </c>
       <c r="G27">
-        <v>-7.759976173994164</v>
+        <v>-7.162710721617631</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.406281015823298</v>
       </c>
       <c r="E28">
-        <v>-32.98537731349744</v>
+        <v>-32.44081472865305</v>
       </c>
       <c r="F28">
-        <v>3.286419126412097</v>
+        <v>3.638322852999772</v>
       </c>
       <c r="G28">
-        <v>-6.336610429930056</v>
+        <v>-8.32760893324868</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.462024310763006</v>
       </c>
       <c r="E29">
-        <v>-31.18554664033387</v>
+        <v>-31.9252592840648</v>
       </c>
       <c r="F29">
-        <v>2.741408047618607</v>
+        <v>3.59348498222104</v>
       </c>
       <c r="G29">
-        <v>-6.755344782464772</v>
+        <v>-8.000374748873881</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.573010990143478</v>
       </c>
       <c r="E30">
-        <v>-32.27300986006183</v>
+        <v>-33.04325573978947</v>
       </c>
       <c r="F30">
-        <v>3.268146998241146</v>
+        <v>3.668432351356728</v>
       </c>
       <c r="G30">
-        <v>-6.653502470040173</v>
+        <v>-7.374039396117007</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.726070935278457</v>
       </c>
       <c r="E31">
-        <v>-32.74968609105722</v>
+        <v>-33.32562873653776</v>
       </c>
       <c r="F31">
-        <v>2.385635845259858</v>
+        <v>3.528479678653752</v>
       </c>
       <c r="G31">
-        <v>-6.722944473271926</v>
+        <v>-7.520580694412847</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.910913054544173</v>
       </c>
       <c r="E32">
-        <v>-32.60037551031332</v>
+        <v>-32.60404131002252</v>
       </c>
       <c r="F32">
-        <v>2.201837685926704</v>
+        <v>3.211907478530281</v>
       </c>
       <c r="G32">
-        <v>-6.598448097722093</v>
+        <v>-7.668313789102823</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.115151024498916</v>
       </c>
       <c r="E33">
-        <v>-33.50882362404406</v>
+        <v>-32.78283904926737</v>
       </c>
       <c r="F33">
-        <v>2.818146347079148</v>
+        <v>3.12095108096809</v>
       </c>
       <c r="G33">
-        <v>-7.685104876078007</v>
+        <v>-7.105474699789172</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.319940783900954</v>
       </c>
       <c r="E34">
-        <v>-31.25394697598273</v>
+        <v>-31.36101368694608</v>
       </c>
       <c r="F34">
-        <v>1.940648473619603</v>
+        <v>2.915171364234248</v>
       </c>
       <c r="G34">
-        <v>-5.799689601643359</v>
+        <v>-7.45247615157896</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.511904482908029</v>
       </c>
       <c r="E35">
-        <v>-32.61470133783659</v>
+        <v>-30.66778356466688</v>
       </c>
       <c r="F35">
-        <v>2.095102546075988</v>
+        <v>3.07900752589474</v>
       </c>
       <c r="G35">
-        <v>-6.792995616882903</v>
+        <v>-7.539993733455133</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.67814227286466</v>
       </c>
       <c r="E36">
-        <v>-30.87867459920409</v>
+        <v>-31.38681013913077</v>
       </c>
       <c r="F36">
-        <v>2.172795124784554</v>
+        <v>3.164897628421409</v>
       </c>
       <c r="G36">
-        <v>-6.650781201606892</v>
+        <v>-7.286667478244563</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.802195228339425</v>
       </c>
       <c r="E37">
-        <v>-30.97639680405261</v>
+        <v>-31.5880894875867</v>
       </c>
       <c r="F37">
-        <v>1.842765267835202</v>
+        <v>2.91671047086865</v>
       </c>
       <c r="G37">
-        <v>-6.914277452714104</v>
+        <v>-6.964958594374806</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.875483010732363</v>
       </c>
       <c r="E38">
-        <v>-30.83973651544914</v>
+        <v>-31.72802386289772</v>
       </c>
       <c r="F38">
-        <v>2.132269734704796</v>
+        <v>2.598733359630031</v>
       </c>
       <c r="G38">
-        <v>-5.976164852705288</v>
+        <v>-6.883807191570652</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.892411108984854</v>
       </c>
       <c r="E39">
-        <v>-28.72634071657245</v>
+        <v>-30.85404196483937</v>
       </c>
       <c r="F39">
-        <v>2.033622774175014</v>
+        <v>2.821325621171092</v>
       </c>
       <c r="G39">
-        <v>-6.502988517097209</v>
+        <v>-6.917644277527542</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.847438249529917</v>
       </c>
       <c r="E40">
-        <v>-31.03470769961238</v>
+        <v>-30.24486258437954</v>
       </c>
       <c r="F40">
-        <v>2.182853161789345</v>
+        <v>2.601283074495848</v>
       </c>
       <c r="G40">
-        <v>-6.208912756843749</v>
+        <v>-7.233175683421019</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.74456689650507</v>
       </c>
       <c r="E41">
-        <v>-28.03400496790977</v>
+        <v>-29.50443217751839</v>
       </c>
       <c r="F41">
-        <v>1.981342850649532</v>
+        <v>2.81548397424655</v>
       </c>
       <c r="G41">
-        <v>-6.42571376311954</v>
+        <v>-7.113876864367842</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.589216488978824</v>
       </c>
       <c r="E42">
-        <v>-29.85418886750081</v>
+        <v>-29.68755460944056</v>
       </c>
       <c r="F42">
-        <v>2.253945309032404</v>
+        <v>2.715688896496488</v>
       </c>
       <c r="G42">
-        <v>-6.395614283076487</v>
+        <v>-7.288246608466794</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.386471118248531</v>
       </c>
       <c r="E43">
-        <v>-28.59227524357537</v>
+        <v>-29.70929128467738</v>
       </c>
       <c r="F43">
-        <v>1.969752333949561</v>
+        <v>2.894223609352254</v>
       </c>
       <c r="G43">
-        <v>-5.807535594571432</v>
+        <v>-7.12814862618764</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.148035057928485</v>
       </c>
       <c r="E44">
-        <v>-28.59542706148471</v>
+        <v>-28.16911651840262</v>
       </c>
       <c r="F44">
-        <v>2.090173760029331</v>
+        <v>2.823895216854576</v>
       </c>
       <c r="G44">
-        <v>-6.158248167910743</v>
+        <v>-7.259345545908957</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.883406270750044</v>
       </c>
       <c r="E45">
-        <v>-26.9347269594958</v>
+        <v>-28.67763245014595</v>
       </c>
       <c r="F45">
-        <v>1.975091990228007</v>
+        <v>3.129201620299973</v>
       </c>
       <c r="G45">
-        <v>-6.926662203576517</v>
+        <v>-6.482370439478627</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.600080186746604</v>
       </c>
       <c r="E46">
-        <v>-26.7649272981042</v>
+        <v>-28.75544974749376</v>
       </c>
       <c r="F46">
-        <v>1.954227072086293</v>
+        <v>2.884720578507338</v>
       </c>
       <c r="G46">
-        <v>-5.721362094184203</v>
+        <v>-6.211230138721239</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.309801992780853</v>
       </c>
       <c r="E47">
-        <v>-27.93726770615791</v>
+        <v>-27.49791968640774</v>
       </c>
       <c r="F47">
-        <v>2.064457922376823</v>
+        <v>3.199781836488102</v>
       </c>
       <c r="G47">
-        <v>-6.208925999025906</v>
+        <v>-7.190840427064819</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.019078930413919</v>
       </c>
       <c r="E48">
-        <v>-26.57115389531598</v>
+        <v>-27.86090404896657</v>
       </c>
       <c r="F48">
-        <v>2.029953106580612</v>
+        <v>2.846433437149945</v>
       </c>
       <c r="G48">
-        <v>-5.497211676811229</v>
+        <v>-6.059027807553246</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.732564324266678</v>
       </c>
       <c r="E49">
-        <v>-26.06887367228122</v>
+        <v>-27.94744771572716</v>
       </c>
       <c r="F49">
-        <v>2.012956664209972</v>
+        <v>2.915696549167623</v>
       </c>
       <c r="G49">
-        <v>-6.801401092007113</v>
+        <v>-6.402023499240515</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.459324963674965</v>
       </c>
       <c r="E50">
-        <v>-24.31156310581267</v>
+        <v>-26.04848648229869</v>
       </c>
       <c r="F50">
-        <v>2.300870665666191</v>
+        <v>2.796666780324556</v>
       </c>
       <c r="G50">
-        <v>-6.300267260999937</v>
+        <v>-6.030792164648802</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.203169385857374</v>
       </c>
       <c r="E51">
-        <v>-26.14532337047871</v>
+        <v>-26.21506639867084</v>
       </c>
       <c r="F51">
-        <v>1.847955817981144</v>
+        <v>2.469161787218938</v>
       </c>
       <c r="G51">
-        <v>-5.957794635507872</v>
+        <v>-5.397448386985292</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.967090143527771</v>
       </c>
       <c r="E52">
-        <v>-24.20576436757147</v>
+        <v>-26.39117422435513</v>
       </c>
       <c r="F52">
-        <v>2.270554075458534</v>
+        <v>2.702536078874837</v>
       </c>
       <c r="G52">
-        <v>-6.423886341981863</v>
+        <v>-5.417857900234899</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.757500744753017</v>
       </c>
       <c r="E53">
-        <v>-25.19308944156781</v>
+        <v>-25.59730103149247</v>
       </c>
       <c r="F53">
-        <v>2.531718436743551</v>
+        <v>2.74274337587192</v>
       </c>
       <c r="G53">
-        <v>-5.927774608557761</v>
+        <v>-5.533677335926301</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.575091915008779</v>
       </c>
       <c r="E54">
-        <v>-25.24220979912901</v>
+        <v>-24.90137873141571</v>
       </c>
       <c r="F54">
-        <v>2.575239203351832</v>
+        <v>3.212760696955165</v>
       </c>
       <c r="G54">
-        <v>-7.371331369865883</v>
+        <v>-5.727284660153959</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.420404345719073</v>
       </c>
       <c r="E55">
-        <v>-25.25992971792103</v>
+        <v>-24.92278482804997</v>
       </c>
       <c r="F55">
-        <v>2.155309945646262</v>
+        <v>3.003988917162411</v>
       </c>
       <c r="G55">
-        <v>-6.106828774594782</v>
+        <v>-6.279076459003062</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.297353213450834</v>
       </c>
       <c r="E56">
-        <v>-25.18976554164618</v>
+        <v>-25.60584173347093</v>
       </c>
       <c r="F56">
-        <v>2.520349922507531</v>
+        <v>2.677219514310479</v>
       </c>
       <c r="G56">
-        <v>-5.614318914717408</v>
+        <v>-5.657786377648039</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.205773707500597</v>
       </c>
       <c r="E57">
-        <v>-22.51429328470045</v>
+        <v>-24.06784063471986</v>
       </c>
       <c r="F57">
-        <v>2.732706876419601</v>
+        <v>3.401197713743996</v>
       </c>
       <c r="G57">
-        <v>-6.520779388825252</v>
+        <v>-6.818665586994412</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.144812850443369</v>
       </c>
       <c r="E58">
-        <v>-22.24892470785096</v>
+        <v>-23.78066292704943</v>
       </c>
       <c r="F58">
-        <v>3.234107724925308</v>
+        <v>3.041427810299338</v>
       </c>
       <c r="G58">
-        <v>-6.545936224378173</v>
+        <v>-6.500962463227174</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.11720236239228</v>
       </c>
       <c r="E59">
-        <v>-22.55591901777895</v>
+        <v>-24.11866822698195</v>
       </c>
       <c r="F59">
-        <v>2.497558221786905</v>
+        <v>3.17489933644281</v>
       </c>
       <c r="G59">
-        <v>-6.086382845344244</v>
+        <v>-5.531743977331367</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.122028900769283</v>
       </c>
       <c r="E60">
-        <v>-22.97717578386848</v>
+        <v>-24.43891285185638</v>
       </c>
       <c r="F60">
-        <v>3.082745119616171</v>
+        <v>3.118119721185321</v>
       </c>
       <c r="G60">
-        <v>-6.322315494291483</v>
+        <v>-6.368368493288285</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.156901760464215</v>
       </c>
       <c r="E61">
-        <v>-21.89326741623655</v>
+        <v>-23.49315916925046</v>
       </c>
       <c r="F61">
-        <v>2.692895539041057</v>
+        <v>2.921198565457017</v>
       </c>
       <c r="G61">
-        <v>-5.793965668405959</v>
+        <v>-6.108252309176669</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.223071688765128</v>
       </c>
       <c r="E62">
-        <v>-20.66008243141577</v>
+        <v>-22.71743610021053</v>
       </c>
       <c r="F62">
-        <v>2.759446576181969</v>
+        <v>2.819049267548199</v>
       </c>
       <c r="G62">
-        <v>-6.807667954712953</v>
+        <v>-6.340036844563202</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.318377362402479</v>
       </c>
       <c r="E63">
-        <v>-21.90701133484983</v>
+        <v>-23.37798196133937</v>
       </c>
       <c r="F63">
-        <v>2.095717194688865</v>
+        <v>3.425223681894793</v>
       </c>
       <c r="G63">
-        <v>-6.976423013577302</v>
+        <v>-6.665499887074492</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.437980436524294</v>
       </c>
       <c r="E64">
-        <v>-21.85200396107866</v>
+        <v>-23.25156508094124</v>
       </c>
       <c r="F64">
-        <v>1.875106387975301</v>
+        <v>3.452162189833833</v>
       </c>
       <c r="G64">
-        <v>-7.480450261385801</v>
+        <v>-6.746502315329379</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.579856160728468</v>
       </c>
       <c r="E65">
-        <v>-22.79289406260034</v>
+        <v>-22.98388245387384</v>
       </c>
       <c r="F65">
-        <v>3.160871762843804</v>
+        <v>2.864185350591939</v>
       </c>
       <c r="G65">
-        <v>-6.439042019460646</v>
+        <v>-7.238191159913014</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.737382478392925</v>
       </c>
       <c r="E66">
-        <v>-22.46383702730699</v>
+        <v>-22.47819681838531</v>
       </c>
       <c r="F66">
-        <v>2.478398083760152</v>
+        <v>2.979306882028597</v>
       </c>
       <c r="G66">
-        <v>-7.791058886062381</v>
+        <v>-6.648275118633664</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.900520612131176</v>
       </c>
       <c r="E67">
-        <v>-21.45937620766562</v>
+        <v>-22.40462270118269</v>
       </c>
       <c r="F67">
-        <v>2.012143207420423</v>
+        <v>2.923585920311885</v>
       </c>
       <c r="G67">
-        <v>-7.756384232084055</v>
+        <v>-6.803238444781408</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.062547570243191</v>
       </c>
       <c r="E68">
-        <v>-21.5097237816829</v>
+        <v>-22.47959611685368</v>
       </c>
       <c r="F68">
-        <v>2.012113386193922</v>
+        <v>3.017996609943751</v>
       </c>
       <c r="G68">
-        <v>-6.787414037103693</v>
+        <v>-6.850996374730935</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.213605770395126</v>
       </c>
       <c r="E69">
-        <v>-21.5085418499669</v>
+        <v>-22.45175958712853</v>
       </c>
       <c r="F69">
-        <v>2.239859749715202</v>
+        <v>2.968183564543805</v>
       </c>
       <c r="G69">
-        <v>-6.626902236632129</v>
+        <v>-6.955516918496805</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.342991550106738</v>
       </c>
       <c r="E70">
-        <v>-20.75603173869029</v>
+        <v>-22.03960958226843</v>
       </c>
       <c r="F70">
-        <v>1.986611267331337</v>
+        <v>3.066080024206651</v>
       </c>
       <c r="G70">
-        <v>-7.154841554870783</v>
+        <v>-7.805989446444494</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.445393536962067</v>
       </c>
       <c r="E71">
-        <v>-21.88133035875233</v>
+        <v>-22.59692434991841</v>
       </c>
       <c r="F71">
-        <v>2.918488147315057</v>
+        <v>2.40612137113109</v>
       </c>
       <c r="G71">
-        <v>-7.245500844463725</v>
+        <v>-6.838323606406605</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.513852188935263</v>
       </c>
       <c r="E72">
-        <v>-21.33276913135917</v>
+        <v>-22.34530422015621</v>
       </c>
       <c r="F72">
-        <v>2.489697015134338</v>
+        <v>2.689620174330388</v>
       </c>
       <c r="G72">
-        <v>-6.770172715935168</v>
+        <v>-7.724440778175627</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.542922045523087</v>
       </c>
       <c r="E73">
-        <v>-21.7371980880362</v>
+        <v>-22.59688359365234</v>
       </c>
       <c r="F73">
-        <v>2.311856474162118</v>
+        <v>2.814995237478898</v>
       </c>
       <c r="G73">
-        <v>-6.165557852461453</v>
+        <v>-6.942314462886191</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.533109676252579</v>
       </c>
       <c r="E74">
-        <v>-22.81268349401386</v>
+        <v>-21.97574904181226</v>
       </c>
       <c r="F74">
-        <v>2.161456431775034</v>
+        <v>2.692797791687526</v>
       </c>
       <c r="G74">
-        <v>-7.867757605116216</v>
+        <v>-6.19378356372928</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.481984445346776</v>
       </c>
       <c r="E75">
-        <v>-22.81444507040285</v>
+        <v>-22.31197012298575</v>
       </c>
       <c r="F75">
-        <v>2.425216896500424</v>
+        <v>2.699588747655677</v>
       </c>
       <c r="G75">
-        <v>-6.654846551529117</v>
+        <v>-6.895493417324279</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.389739997193938</v>
       </c>
       <c r="E76">
-        <v>-21.73604785563825</v>
+        <v>-22.92940038308756</v>
       </c>
       <c r="F76">
-        <v>1.942055041469557</v>
+        <v>2.603165125235009</v>
       </c>
       <c r="G76">
-        <v>-7.099052241442986</v>
+        <v>-6.596617366038876</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.261001165474634</v>
       </c>
       <c r="E77">
-        <v>-21.66712900971552</v>
+        <v>-22.68608547465543</v>
       </c>
       <c r="F77">
-        <v>1.850078095267117</v>
+        <v>2.322530816514592</v>
       </c>
       <c r="G77">
-        <v>-6.461540486945533</v>
+        <v>-6.784987407223407</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.096636133553742</v>
       </c>
       <c r="E78">
-        <v>-22.48473593485238</v>
+        <v>-23.45326331324288</v>
       </c>
       <c r="F78">
-        <v>1.64580600720637</v>
+        <v>2.226826216999554</v>
       </c>
       <c r="G78">
-        <v>-6.558135584690388</v>
+        <v>-6.975562271737092</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.900731282713891</v>
       </c>
       <c r="E79">
-        <v>-21.35701910967025</v>
+        <v>-24.45724411463943</v>
       </c>
       <c r="F79">
-        <v>1.977393194872984</v>
+        <v>2.406197580932148</v>
       </c>
       <c r="G79">
-        <v>-6.609508630368798</v>
+        <v>-6.80909148929484</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.680711491055392</v>
       </c>
       <c r="E80">
-        <v>-23.14830681661834</v>
+        <v>-23.25784607438988</v>
       </c>
       <c r="F80">
-        <v>1.359600099334724</v>
+        <v>2.315516201347686</v>
       </c>
       <c r="G80">
-        <v>-5.994031866980735</v>
+        <v>-6.301912602132955</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.439345664821295</v>
       </c>
       <c r="E81">
-        <v>-23.27167603400931</v>
+        <v>-24.76931484393002</v>
       </c>
       <c r="F81">
-        <v>1.934811796899478</v>
+        <v>2.22655285575663</v>
       </c>
       <c r="G81">
-        <v>-6.274835650167256</v>
+        <v>-6.343529470107133</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.18335030557211</v>
       </c>
       <c r="E82">
-        <v>-23.62759144864216</v>
+        <v>-25.51098831690627</v>
       </c>
       <c r="F82">
-        <v>1.271239805212906</v>
+        <v>1.910540631997452</v>
       </c>
       <c r="G82">
-        <v>-5.383030961161766</v>
+        <v>-6.200553629357089</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.921725985400764</v>
       </c>
       <c r="E83">
-        <v>-25.22687638613904</v>
+        <v>-25.85936382231635</v>
       </c>
       <c r="F83">
-        <v>1.127097250186569</v>
+        <v>1.91334217055372</v>
       </c>
       <c r="G83">
-        <v>-4.513605560001749</v>
+        <v>-5.590019510459157</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.658235997275837</v>
       </c>
       <c r="E84">
-        <v>-25.45613491125136</v>
+        <v>-25.62586211705884</v>
       </c>
       <c r="F84">
-        <v>1.24658096436637</v>
+        <v>2.105624468826347</v>
       </c>
       <c r="G84">
-        <v>-5.367262832758217</v>
+        <v>-5.501528628194439</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.400462075450035</v>
       </c>
       <c r="E85">
-        <v>-23.99385442638254</v>
+        <v>-27.75427659998196</v>
       </c>
       <c r="F85">
-        <v>1.712191370866722</v>
+        <v>2.063409209244879</v>
       </c>
       <c r="G85">
-        <v>-5.231762203835848</v>
+        <v>-6.532286845119758</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.157609916951262</v>
       </c>
       <c r="E86">
-        <v>-26.59617371420836</v>
+        <v>-28.19810780899973</v>
       </c>
       <c r="F86">
-        <v>0.705934553418231</v>
+        <v>1.547561633234348</v>
       </c>
       <c r="G86">
-        <v>-5.484048947747087</v>
+        <v>-5.42334678473901</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.933687987534605</v>
       </c>
       <c r="E87">
-        <v>-27.7623870969297</v>
+        <v>-29.50996144428175</v>
       </c>
       <c r="F87">
-        <v>0.6300262780952954</v>
+        <v>1.519899132185262</v>
       </c>
       <c r="G87">
-        <v>-6.069042207809542</v>
+        <v>-5.532376291529368</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.736428266637029</v>
       </c>
       <c r="E88">
-        <v>-27.60102851108839</v>
+        <v>-29.39387854156913</v>
       </c>
       <c r="F88">
-        <v>0.6507743964332147</v>
+        <v>1.318317581448808</v>
       </c>
       <c r="G88">
-        <v>-5.144906731067529</v>
+        <v>-6.045663135211208</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.57678300771923</v>
       </c>
       <c r="E89">
-        <v>-29.12996360487611</v>
+        <v>-30.95158982343859</v>
       </c>
       <c r="F89">
-        <v>0.5396712752675366</v>
+        <v>1.557599789421473</v>
       </c>
       <c r="G89">
-        <v>-4.2740809691444</v>
+        <v>-5.280169000711071</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.460994240835265</v>
       </c>
       <c r="E90">
-        <v>-30.04248281673974</v>
+        <v>-32.5030676608365</v>
       </c>
       <c r="F90">
-        <v>0.8920728506642939</v>
+        <v>1.073810031899283</v>
       </c>
       <c r="G90">
-        <v>-6.427693469352024</v>
+        <v>-5.69748312920944</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.396557880475735</v>
       </c>
       <c r="E91">
-        <v>-34.19577728134862</v>
+        <v>-32.83216771663293</v>
       </c>
       <c r="F91">
-        <v>0.05943355716855118</v>
+        <v>1.000350410619023</v>
       </c>
       <c r="G91">
-        <v>-5.948624424364091</v>
+        <v>-5.543754636547843</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.39405811607417</v>
       </c>
       <c r="E92">
-        <v>-34.19388664345042</v>
+        <v>-35.38671613215184</v>
       </c>
       <c r="F92">
-        <v>0.2608817407531546</v>
+        <v>1.039888386754643</v>
       </c>
       <c r="G92">
-        <v>-5.993604806606169</v>
+        <v>-5.534190470484888</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.456632802231408</v>
       </c>
       <c r="E93">
-        <v>-34.99641148590474</v>
+        <v>-36.60184382686703</v>
       </c>
       <c r="F93">
-        <v>0.5594328080287215</v>
+        <v>1.020005912352649</v>
       </c>
       <c r="G93">
-        <v>-6.05873316900025</v>
+        <v>-5.453370122234661</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.584685669946694</v>
       </c>
       <c r="E94">
-        <v>-38.44409271606044</v>
+        <v>-38.61855670567995</v>
       </c>
       <c r="F94">
-        <v>-0.5588772679964586</v>
+        <v>0.7243582728238948</v>
       </c>
       <c r="G94">
-        <v>-6.816106535292556</v>
+        <v>-4.896192065793163</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.780506157453313</v>
       </c>
       <c r="E95">
-        <v>-38.73089003191422</v>
+        <v>-39.86462972752656</v>
       </c>
       <c r="F95">
-        <v>-0.3676660487756515</v>
+        <v>0.2327851751850009</v>
       </c>
       <c r="G95">
-        <v>-5.28725687871065</v>
+        <v>-4.73304507107234</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.039922929448853</v>
       </c>
       <c r="E96">
-        <v>-39.53433868306611</v>
+        <v>-42.52181147795531</v>
       </c>
       <c r="F96">
-        <v>-1.198640323791767</v>
+        <v>0.2737081816181021</v>
       </c>
       <c r="G96">
-        <v>-5.336057630505047</v>
+        <v>-6.098155145281892</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.347966197010944</v>
       </c>
       <c r="E97">
-        <v>-41.73144105973757</v>
+        <v>-43.18072935267838</v>
       </c>
       <c r="F97">
-        <v>-0.7796620318646108</v>
+        <v>-0.4242783338177754</v>
       </c>
       <c r="G97">
-        <v>-6.512423571884131</v>
+        <v>-5.653704474998118</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.703862925964406</v>
       </c>
       <c r="E98">
-        <v>-45.06255484046184</v>
+        <v>-44.86549829401806</v>
       </c>
       <c r="F98">
-        <v>-0.9077408862158592</v>
+        <v>-0.4188210493681322</v>
       </c>
       <c r="G98">
-        <v>-6.262550215671021</v>
+        <v>-5.296592617131395</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.078494594753961</v>
       </c>
       <c r="E99">
-        <v>-46.3423129162145</v>
+        <v>-47.13001606324171</v>
       </c>
       <c r="F99">
-        <v>-1.767944105039755</v>
+        <v>-0.79837733659606</v>
       </c>
       <c r="G99">
-        <v>-7.348468742371677</v>
+        <v>-6.092974141512933</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.47038565686919</v>
       </c>
       <c r="E100">
-        <v>-47.95356887475065</v>
+        <v>-50.01414002432786</v>
       </c>
       <c r="F100">
-        <v>-1.471642883630192</v>
+        <v>-1.284255408340707</v>
       </c>
       <c r="G100">
-        <v>-6.051271199354733</v>
+        <v>-5.920882052744998</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.834725169062892</v>
       </c>
       <c r="E101">
-        <v>-50.57597760539301</v>
+        <v>-50.58748106149099</v>
       </c>
       <c r="F101">
-        <v>-1.785656256846414</v>
+        <v>-1.386829658727162</v>
       </c>
       <c r="G101">
-        <v>-5.433871009008353</v>
+        <v>-6.958552688756316</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.199856468000894</v>
       </c>
       <c r="E102">
-        <v>-52.86433099755603</v>
+        <v>-53.50007101018935</v>
       </c>
       <c r="F102">
-        <v>-2.447563230053359</v>
+        <v>-1.596637726140818</v>
       </c>
       <c r="G102">
-        <v>-6.827325974125146</v>
+        <v>-7.067797381006726</v>
       </c>
     </row>
   </sheetData>
